--- a/reporting/audit/CTS - Discretionary Technology Spend - FY2027 YTD.xlsx
+++ b/reporting/audit/CTS - Discretionary Technology Spend - FY2027 YTD.xlsx
@@ -192,7 +192,7 @@
     <t xml:space="preserve">Note 4 - period covered</t>
   </si>
   <si>
-    <t xml:space="preserve">Actual amounts cover 2 months of a twelve month financial year. The annualised run rate column extrapolates the year-to-date actual evenly across twelve months. It is an arithmetic extrapolation only and makes no allowance for seasonality, timing of renewals or known future commitments.</t>
+    <t xml:space="preserve">These figures cover July and August only, which is 2 months of a twelve month year. The annualised run rate column takes what has been spent so far, divides it by 2 and multiplies by twelve, so it assumes the rest of the year looks like the first 2 months. It makes no allowance for quieter or busier periods, for annual renewals that fall due later in the year, or for spending already committed but not yet incurred. Treat it as a rough indicator, not a forecast.</t>
   </si>
   <si>
     <t xml:space="preserve">Supplier analysis</t>
@@ -2652,7 +2652,7 @@
       <c r="H19" s="21"/>
       <c r="I19" s="21"/>
     </row>
-    <row r="20" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
         <v>51</v>
       </c>
